--- a/ordenes/management/commands/bd.xlsx
+++ b/ordenes/management/commands/bd.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dcarr\Desktop\ProG\genesis\ordenes\management\commands\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9086B89E-E9E5-4F06-8FC7-7F1B2D08C4FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{689B0287-55E1-4F19-93EF-10F23FC0FCC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="29">
   <si>
     <t>LISTADO DE ORDENES DE TRABAJOS</t>
   </si>
@@ -98,6 +98,15 @@
   </si>
   <si>
     <t>Fecha Entrega</t>
+  </si>
+  <si>
+    <t>PRUEBA</t>
+  </si>
+  <si>
+    <t>Prueba</t>
+  </si>
+  <si>
+    <t>Pruewba</t>
   </si>
 </sst>
 </file>
@@ -496,7 +505,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A3:M11"/>
+  <dimension ref="A3:M12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.88671875" bestFit="1" customWidth="1"/>
@@ -697,6 +706,38 @@
         <v>46115</v>
       </c>
     </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
+        <v>46104</v>
+      </c>
+      <c r="B12">
+        <v>20250006</v>
+      </c>
+      <c r="C12">
+        <v>20251291</v>
+      </c>
+      <c r="D12" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" t="s">
+        <v>28</v>
+      </c>
+      <c r="G12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12" s="3">
+        <v>46172</v>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
